--- a/new-stats/sevilla-fc.xlsx
+++ b/new-stats/sevilla-fc.xlsx
@@ -1903,22 +1903,62 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>22/02/2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M26" t="n">
+        <v>6</v>
+      </c>
+      <c r="N26" t="n">
+        <v>6</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>

--- a/new-stats/sevilla-fc.xlsx
+++ b/new-stats/sevilla-fc.xlsx
@@ -1961,22 +1961,62 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>01/03/2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M27" t="n">
+        <v>14</v>
+      </c>
+      <c r="N27" t="n">
+        <v>9</v>
+      </c>
+      <c r="O27" t="n">
+        <v>6</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>

--- a/new-stats/sevilla-fc.xlsx
+++ b/new-stats/sevilla-fc.xlsx
@@ -2019,22 +2019,62 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>08/03/2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M28" t="n">
+        <v>11</v>
+      </c>
+      <c r="N28" t="n">
+        <v>9</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>

--- a/new-stats/sevilla-fc.xlsx
+++ b/new-stats/sevilla-fc.xlsx
@@ -2077,22 +2077,62 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>15/03/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="M29" t="n">
+        <v>9</v>
+      </c>
+      <c r="N29" t="n">
+        <v>13</v>
+      </c>
+      <c r="O29" t="n">
+        <v>4</v>
+      </c>
+      <c r="P29" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>

--- a/new-stats/sevilla-fc.xlsx
+++ b/new-stats/sevilla-fc.xlsx
@@ -2135,22 +2135,62 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>21/03/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M30" t="n">
+        <v>13</v>
+      </c>
+      <c r="N30" t="n">
+        <v>9</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>

--- a/new-stats/sevilla-fc.xlsx
+++ b/new-stats/sevilla-fc.xlsx
@@ -2193,22 +2193,62 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Oviedo</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M31" t="n">
+        <v>9</v>
+      </c>
+      <c r="N31" t="n">
+        <v>7</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>

--- a/new-stats/sevilla-fc.xlsx
+++ b/new-stats/sevilla-fc.xlsx
@@ -2251,22 +2251,62 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M32" t="n">
+        <v>11</v>
+      </c>
+      <c r="N32" t="n">
+        <v>13</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>

--- a/new-stats/sevilla-fc.xlsx
+++ b/new-stats/sevilla-fc.xlsx
@@ -2309,40 +2309,120 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M33" t="n">
+        <v>7</v>
+      </c>
+      <c r="N33" t="n">
+        <v>8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M34" t="n">
+        <v>8</v>
+      </c>
+      <c r="N34" t="n">
+        <v>15</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2</v>
+      </c>
+      <c r="P34" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>

--- a/new-stats/sevilla-fc.xlsx
+++ b/new-stats/sevilla-fc.xlsx
@@ -2425,22 +2425,62 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="M35" t="n">
+        <v>19</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>

--- a/new-stats/sevilla-fc.xlsx
+++ b/new-stats/sevilla-fc.xlsx
@@ -2483,22 +2483,62 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M36" t="n">
+        <v>21</v>
+      </c>
+      <c r="N36" t="n">
+        <v>10</v>
+      </c>
+      <c r="O36" t="n">
+        <v>6</v>
+      </c>
+      <c r="P36" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>

--- a/new-stats/sevilla-fc.xlsx
+++ b/new-stats/sevilla-fc.xlsx
@@ -2541,40 +2541,120 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M37" t="n">
+        <v>13</v>
+      </c>
+      <c r="N37" t="n">
+        <v>6</v>
+      </c>
+      <c r="O37" t="n">
+        <v>5</v>
+      </c>
+      <c r="P37" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="M38" t="n">
+        <v>14</v>
+      </c>
+      <c r="N38" t="n">
+        <v>12</v>
+      </c>
+      <c r="O38" t="n">
+        <v>6</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>

--- a/new-stats/sevilla-fc.xlsx
+++ b/new-stats/sevilla-fc.xlsx
@@ -2657,22 +2657,62 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M39" t="n">
+        <v>9</v>
+      </c>
+      <c r="N39" t="n">
+        <v>12</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
